--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -912,7 +912,7 @@
     <t>Voie d'administration</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260916095454</t>
   </si>
   <si>
     <t>SubstanceAdministration.approachSiteCode</t>
@@ -924,7 +924,7 @@
     <t>Région anatomique d'administration</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260916095452</t>
   </si>
   <si>
     <t>SubstanceAdministration.doseQuantity</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -956,56 +956,56 @@
     <t>SubstanceAdministration.consumable</t>
   </si>
   <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
+</t>
+  </si>
+  <si>
+    <t>Vaccin</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.realmCode</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.displayable</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.root</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.extension</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.templateId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeCode</t>
+  </si>
+  <si>
+    <t>CSM</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
+  </si>
+  <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-produit-de-sante|0.1.0}
 </t>
   </si>
   <si>
-    <t>Vaccin</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.realmCode</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.displayable</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.root</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.extension</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.templateId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeCode</t>
-  </si>
-  <si>
-    <t>CSM</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct
-</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.subject</t>
   </si>
   <si>
@@ -1061,8 +1061,8 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
+    <t>profile:supply}
+profile:observation}profile:act}profile:substanceAdministration}</t>
   </si>
   <si>
     <t>SubstanceAdministration.entryRelationship:frPrescription</t>
@@ -2049,7 +2049,7 @@
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="80.5" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="51.7890625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -13458,7 +13458,7 @@
         <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>75</v>
@@ -13656,7 +13656,7 @@
         <v>81</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>75</v>
@@ -14151,7 +14151,7 @@
         <v>81</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>75</v>
@@ -15965,7 +15965,7 @@
         <v>81</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>75</v>
@@ -16658,7 +16658,7 @@
         <v>81</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>75</v>
@@ -16757,7 +16757,7 @@
         <v>81</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>75</v>
@@ -18472,7 +18472,7 @@
         <v>81</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>75</v>
@@ -19165,7 +19165,7 @@
         <v>81</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>75</v>
@@ -19264,7 +19264,7 @@
         <v>81</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>75</v>
@@ -21177,7 +21177,7 @@
         <v>81</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>75</v>
@@ -21672,7 +21672,7 @@
         <v>81</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>75</v>
@@ -21771,7 +21771,7 @@
         <v>81</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>75</v>
@@ -23486,7 +23486,7 @@
         <v>81</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>75</v>
@@ -23684,7 +23684,7 @@
         <v>81</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>75</v>
@@ -24278,7 +24278,7 @@
         <v>81</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H221" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
